--- a/config/MB300L_thresholds.xlsx
+++ b/config/MB300L_thresholds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescopiscitelli/Documents/PYTHON/MBUTYcap/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescopiscitelli/git_repos/mbuty/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C62E25-AC7D-D341-B7D9-8E8E4B158FCC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AB5D14-1477-3A4D-ACD6-9AA3CFE8749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="460" windowWidth="25240" windowHeight="16540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-39560" yWindow="600" windowWidth="37540" windowHeight="26360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -180,7 +180,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -286,7 +286,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -428,7 +428,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="2">
         <v>2</v>

--- a/config/MB300L_thresholds.xlsx
+++ b/config/MB300L_thresholds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francescopiscitelli/git_repos/mbuty/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AB5D14-1477-3A4D-ACD6-9AA3CFE8749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F9F0A1-228E-6F48-8A21-B5F8D1679EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-39560" yWindow="600" windowWidth="37540" windowHeight="26360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,7 +488,7 @@
         <v>5000</v>
       </c>
       <c r="G2" s="3">
-        <v>7000</v>
+        <v>1200</v>
       </c>
       <c r="H2" s="3">
         <v>10500</v>
@@ -514,7 +514,7 @@
         <v>15000</v>
       </c>
       <c r="G3" s="3">
-        <v>7000</v>
+        <v>1200</v>
       </c>
       <c r="H3" s="3">
         <v>18500</v>
@@ -540,7 +540,7 @@
         <v>14000</v>
       </c>
       <c r="G4" s="3">
-        <v>7000</v>
+        <v>1200</v>
       </c>
       <c r="H4" s="3">
         <v>19500</v>
@@ -566,7 +566,7 @@
         <v>15000</v>
       </c>
       <c r="G5" s="3">
-        <v>7000</v>
+        <v>1200</v>
       </c>
       <c r="H5" s="3">
         <v>19500</v>
@@ -592,7 +592,7 @@
         <v>16000</v>
       </c>
       <c r="G6" s="3">
-        <v>7000</v>
+        <v>1200</v>
       </c>
       <c r="H6" s="3">
         <v>21500</v>
@@ -618,7 +618,7 @@
         <v>10000</v>
       </c>
       <c r="G7" s="3">
-        <v>7000</v>
+        <v>1200</v>
       </c>
       <c r="H7" s="3">
         <v>15000</v>
@@ -644,7 +644,7 @@
         <v>15000</v>
       </c>
       <c r="G8" s="3">
-        <v>12195.121951219511</v>
+        <v>500</v>
       </c>
       <c r="H8" s="3">
         <v>19744.483159117302</v>
@@ -670,7 +670,7 @@
         <v>17000</v>
       </c>
       <c r="G9" s="3">
-        <v>11904.761904761903</v>
+        <v>500</v>
       </c>
       <c r="H9" s="3">
         <v>19274.376417233558</v>
@@ -696,7 +696,7 @@
         <v>16279.069767441859</v>
       </c>
       <c r="G10" s="3">
-        <v>11627.906976744185</v>
+        <v>500</v>
       </c>
       <c r="H10" s="3">
         <v>18826.13510520487</v>
@@ -722,7 +722,7 @@
         <v>15909.09090909091</v>
       </c>
       <c r="G11" s="3">
-        <v>11363.636363636364</v>
+        <v>500</v>
       </c>
       <c r="H11" s="3">
         <v>18398.268398268399</v>
@@ -748,7 +748,7 @@
         <v>15555.555555555555</v>
       </c>
       <c r="G12" s="3">
-        <v>11111.111111111111</v>
+        <v>500</v>
       </c>
       <c r="H12" s="3">
         <v>18888.888888888887</v>
@@ -774,7 +774,7 @@
         <v>15217.391304347826</v>
       </c>
       <c r="G13" s="3">
-        <v>12000</v>
+        <v>500</v>
       </c>
       <c r="H13" s="3">
         <v>18478.260869565216</v>
@@ -800,7 +800,7 @@
         <v>14893.617021276596</v>
       </c>
       <c r="G14" s="3">
-        <v>14000</v>
+        <v>500</v>
       </c>
       <c r="H14" s="3">
         <v>18500</v>
@@ -826,7 +826,7 @@
         <v>15500</v>
       </c>
       <c r="G15" s="3">
-        <v>14000</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
         <v>18500</v>
@@ -852,7 +852,7 @@
         <v>14285.714285714286</v>
       </c>
       <c r="G16" s="3">
-        <v>12000</v>
+        <v>500</v>
       </c>
       <c r="H16" s="3">
         <v>16500</v>
@@ -878,7 +878,7 @@
         <v>13000</v>
       </c>
       <c r="G17" s="3">
-        <v>12000</v>
+        <v>500</v>
       </c>
       <c r="H17" s="3">
         <v>18000</v>
@@ -904,7 +904,7 @@
         <v>13725.490196078432</v>
       </c>
       <c r="G18" s="3">
-        <v>12000</v>
+        <v>500</v>
       </c>
       <c r="H18" s="3">
         <v>17000</v>
@@ -930,7 +930,7 @@
         <v>13461.538461538461</v>
       </c>
       <c r="G19" s="3">
-        <v>12000</v>
+        <v>500</v>
       </c>
       <c r="H19" s="3">
         <v>15000</v>
@@ -956,7 +956,7 @@
         <v>13207.54716981132</v>
       </c>
       <c r="G20" s="3">
-        <v>12500</v>
+        <v>500</v>
       </c>
       <c r="H20" s="3">
         <v>15000</v>
@@ -982,7 +982,7 @@
         <v>14000</v>
       </c>
       <c r="G21" s="3">
-        <v>12000</v>
+        <v>500</v>
       </c>
       <c r="H21" s="3">
         <v>15500</v>
@@ -1008,7 +1008,7 @@
         <v>12727.272727272726</v>
       </c>
       <c r="G22" s="3">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>18500</v>
@@ -1034,7 +1034,7 @@
         <v>12499.999999999998</v>
       </c>
       <c r="G23" s="3">
-        <v>12500</v>
+        <v>500</v>
       </c>
       <c r="H23" s="3">
         <v>15178.571428571428</v>
@@ -1060,7 +1060,7 @@
         <v>12280.701754385964</v>
       </c>
       <c r="G24" s="3">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>13000</v>
@@ -1086,7 +1086,7 @@
         <v>12068.965517241379</v>
       </c>
       <c r="G25" s="3">
-        <v>12500</v>
+        <v>500</v>
       </c>
       <c r="H25" s="3">
         <v>13500</v>
@@ -1112,7 +1112,7 @@
         <v>11864.406779661016</v>
       </c>
       <c r="G26" s="3">
-        <v>12000</v>
+        <v>500</v>
       </c>
       <c r="H26" s="3">
         <v>14406.779661016948</v>
@@ -1138,7 +1138,7 @@
         <v>11666.666666666664</v>
       </c>
       <c r="G27" s="3">
-        <v>13000</v>
+        <v>1000</v>
       </c>
       <c r="H27" s="3">
         <v>14166.666666666664</v>
@@ -1164,7 +1164,7 @@
         <v>11475.409836065573</v>
       </c>
       <c r="G28" s="3">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="H28" s="3">
         <v>15000</v>
@@ -1190,7 +1190,7 @@
         <v>11290.322580645161</v>
       </c>
       <c r="G29" s="3">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="H29" s="3">
         <v>13709.677419354839</v>
@@ -1216,7 +1216,7 @@
         <v>11111.111111111111</v>
       </c>
       <c r="G30" s="3">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="H30" s="3">
         <v>13492.063492063491</v>
@@ -1242,7 +1242,7 @@
         <v>10937.5</v>
       </c>
       <c r="G31" s="3">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="H31" s="3">
         <v>13281.25</v>
@@ -1268,7 +1268,7 @@
         <v>10769.23076923077</v>
       </c>
       <c r="G32" s="3">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="H32" s="3">
         <v>13076.923076923076</v>
@@ -1294,7 +1294,7 @@
         <v>20000</v>
       </c>
       <c r="G33" s="3">
-        <v>20000</v>
+        <v>500</v>
       </c>
       <c r="H33" s="3">
         <v>20000</v>
